--- a/reports/jobs_2026-08-20.xlsx
+++ b/reports/jobs_2026-08-20.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -525,12 +525,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Agoda Tech – Software Engineering &amp; Engineering Management roles (Hywel) Information Technology Bangkok, Thailand</t>
+          <t>International Payroll Partner (Bangkok-based, Relocation Provided) People and Organization Development Bangkok, Thailand</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/job/8120906-agoda-tech-software-engineering-engineering-management-roles-hywel/</t>
+          <t>https://careersatagoda.com/job/8063978-international-payroll-partner-bangkok-based-relocation-provided/</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -1013,12 +1013,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlan</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Theorem Proving Engineer</t>
+          <t>Field Security Engineer</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1031,7 +1031,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -1039,12 +1043,12 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
+          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://jobs.ashbyhq.com/atlan</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1056,17 +1060,17 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Embedded Compiler Engineer (Machine Learning)</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1082,12 +1086,12 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/lund/embedded-compiler-engineer-machine-learning/33099/94847322016</t>
+          <t>https://www.atlassian.com/company/careers/engineering</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1099,17 +1103,17 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Atlan</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Field Security Engineer</t>
+          <t>AI and Machine Learning</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1117,11 +1121,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
+          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1146,12 +1146,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Booking.com India</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Web Engineer</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1164,7 +1164,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Remote job</t>
+        </is>
+      </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -1172,12 +1176,12 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering</t>
+          <t>https://careers.tellent.com/o/web-engineer</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://jobs.recruitee.com</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1189,17 +1193,17 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Cisco India</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AI and Machine Learning</t>
+          <t>Web Engineer</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1207,7 +1211,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Remote job</t>
+        </is>
+      </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -1215,12 +1223,12 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
+          <t>https://careers.tellent.com/o/web-engineer</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://jobs.recruitee.com</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1232,12 +1240,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Booking.com India</t>
+          <t>Cloudflare India</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Web Engineer</t>
+          <t>Customer Engineer, India (Based in Mumbai)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1252,7 +1260,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Remote job</t>
+          <t>Remote India</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1262,12 +1270,12 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://careers.tellent.com/o/web-engineer</t>
+          <t>https://boards.greenhouse.io/cloudflare/jobs/7955378?gh_jid=7955378</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.recruitee.com</t>
+          <t>https://boards.greenhouse.io/cloudflare</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1279,7 +1287,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Cisco India</t>
+          <t>Elastic India</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1326,12 +1334,12 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Cloudflare India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Customer Engineer, India (Based in Mumbai)</t>
+          <t>Implementation Engineer</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1346,7 +1354,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Remote India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1356,12 +1364,12 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/cloudflare/jobs/7955378?gh_jid=7955378</t>
+          <t>https://exotel.com/about-us/careers/#op-575251-implementation-engineer</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/cloudflare</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1373,12 +1381,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Elastic India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Web Engineer</t>
+          <t>Implementation Engineer</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1393,7 +1401,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Remote job</t>
+          <t>Gurgaon Full-time</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1403,12 +1411,12 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://careers.tellent.com/o/web-engineer</t>
+          <t>https://exotel.com/about-us/careers/#op-689879-implementation-engineer-</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.recruitee.com</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1425,12 +1433,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer</t>
+          <t>Integration &amp; Customisation Engineer (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1440,7 +1448,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1450,7 +1458,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-575251-implementation-engineer</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-php--reactjs</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1472,12 +1480,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1485,11 +1493,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Gurgaon Full-time</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -1497,7 +1501,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-689879-implementation-engineer-</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1519,12 +1523,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer (PHP + React.JS)</t>
+          <t>Tech Support Intern</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1534,7 +1538,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1544,7 +1548,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-php--reactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-698555-tech-support-intern</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1566,12 +1570,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>Product Support Intern (API Integration)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1579,7 +1583,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -1587,7 +1595,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-685404-product-support-intern-api-integration</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1609,12 +1617,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Tech Support Intern</t>
+          <t>Software Engineer 3 (Full Stack)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1634,7 +1642,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-698555-tech-support-intern</t>
+          <t>https://exotel.com/about-us/careers/#op-697293-software-engineer-3-full-stack</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1656,12 +1664,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Product Support Intern (API Integration)</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1671,7 +1679,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1681,7 +1689,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-685404-product-support-intern-api-integration</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1703,12 +1711,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 (Full Stack)</t>
+          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1718,7 +1726,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bengaluru Full-time</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1728,7 +1736,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-697293-software-engineer-3-full-stack</t>
+          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1750,12 +1758,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Software Developer - 3 (Golang/Java/Python)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1765,7 +1773,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1775,7 +1783,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1797,7 +1805,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1812,7 +1820,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1822,7 +1830,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1844,12 +1852,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Golang/Java/Python)</t>
+          <t>Software Engineer - 3 (Gen AI &amp; Speech)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1859,7 +1867,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore Full-time</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1869,7 +1877,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
+          <t>https://exotel.com/about-us/careers/#op-694350-software-engineer-3-gen-ai--speech</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1891,12 +1899,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1916,7 +1924,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1933,17 +1941,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Gen AI &amp; Speech)</t>
+          <t>Ai Engg Intern</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1953,7 +1961,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Bangalore Full-time</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1963,12 +1971,12 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-694350-software-engineer-3-gen-ai--speech</t>
+          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -1980,17 +1988,17 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2000,7 +2008,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2010,12 +2018,12 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2032,7 +2040,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Ai Engg Intern</t>
+          <t>GenAI Product Builder Intern</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2057,7 +2065,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
+          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2074,17 +2082,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Freshworks</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>Specialist - Data Platform Engineering</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2094,7 +2102,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Chennai, in</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -2104,12 +2112,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://careers.smartrecruiters.com/Freshworks</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2121,12 +2129,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>GenAI Product Builder Intern</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2139,11 +2147,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -2151,12 +2155,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2168,17 +2172,17 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Freshworks</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Specialist - Data Platform Engineering</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2186,11 +2190,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>Chennai, in</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/Freshworks/postings/744000143102264</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/Freshworks</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2215,17 +2215,17 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2233,7 +2233,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -2241,12 +2245,12 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2258,12 +2262,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2276,7 +2280,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>New Delhi, in</t>
+        </is>
+      </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -2284,12 +2292,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2301,17 +2309,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Machine Learning Engineer (Agent Intelligence &amp; Evaluations)</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2321,7 +2329,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2331,12 +2339,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143976319</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2353,12 +2361,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t xml:space="preserve"> Software Engineer - 2 Backend</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2368,7 +2376,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2378,7 +2386,7 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143738909</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -2395,17 +2403,17 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (Agent Intelligence &amp; Evaluations)</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2415,7 +2423,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2425,12 +2433,12 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143976319</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2442,17 +2450,17 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Licious</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Software Engineer - 2 Backend</t>
+          <t>By: Licious DevOps</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2460,11 +2468,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -2472,12 +2476,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000143738909</t>
+          <t>https://careers.licious.com/author/adminlic/</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://www.licious.in/careers</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2489,17 +2493,17 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2507,11 +2511,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2536,17 +2536,17 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Licious</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>By: Licious DevOps</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://careers.licious.com/author/adminlic/</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://www.licious.in/careers</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2579,17 +2579,17 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Automation engineer (Warehouse Automation)</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2597,7 +2597,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -2605,12 +2609,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://jobs.lever.co/meesho/fe839191-1761-4094-9d3c-4d554904b84d</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2622,12 +2626,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>GTM Engineer – Meesho AI Services (MAS)</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2640,7 +2644,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -2648,12 +2656,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://jobs.lever.co/meesho/c49e13f6-f027-42f3-98b5-745d83997cbf</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2670,12 +2678,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Automation engineer (Warehouse Automation)</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2695,7 +2703,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/fe839191-1761-4094-9d3c-4d554904b84d</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -2712,12 +2720,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Microsoft India</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>GTM Engineer – Meesho AI Services (MAS)</t>
+          <t>Web Engineer</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2732,7 +2740,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Remote job</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -2742,12 +2750,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c49e13f6-f027-42f3-98b5-745d83997cbf</t>
+          <t>https://careers.tellent.com/o/web-engineer</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://jobs.recruitee.com</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2759,12 +2767,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2777,11 +2785,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
       <c r="F51" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -2789,12 +2793,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -2806,17 +2810,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Microsoft India</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Web Engineer</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2824,11 +2828,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Remote job</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
       <c r="F52" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://careers.tellent.com/o/web-engineer</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.recruitee.com</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2853,17 +2853,17 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -2896,17 +2896,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Palo Alto Networks India</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Web Engineer</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2914,7 +2914,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Remote job</t>
+        </is>
+      </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -2922,12 +2926,12 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://careers.tellent.com/o/web-engineer</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://jobs.recruitee.com</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -2939,12 +2943,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>Admin &amp; Operations - Internship</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2957,7 +2961,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -2965,12 +2973,12 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://jobs.lever.co/paytm/6c1b9af2-9a7c-4cd2-a97b-54e956cf82f1</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -2982,17 +2990,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Palo Alto Networks India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Web Engineer</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3002,7 +3010,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Remote job</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -3012,12 +3020,12 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://careers.tellent.com/o/web-engineer</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.recruitee.com</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -3034,7 +3042,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Operations - Internship</t>
+          <t>Product Management - Intern</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3059,7 +3067,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/6c1b9af2-9a7c-4cd2-a97b-54e956cf82f1</t>
+          <t>https://jobs.lever.co/paytm/1155c0e3-bf03-4b46-97f0-44673b6518f7</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3081,7 +3089,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Product Management - Intern - Telco.</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3096,7 +3104,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3106,7 +3114,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3128,7 +3136,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Product Management - Intern</t>
+          <t>Product Management Intern- Insurance</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3138,7 +3146,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>recent graduate</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -3153,7 +3161,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/1155c0e3-bf03-4b46-97f0-44673b6518f7</t>
+          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3175,7 +3183,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Product Management - Intern - Telco.</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3200,7 +3208,7 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
+          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -3217,27 +3225,27 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>PhonePe</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Product Management Intern- Insurance</t>
+          <t>AI Video Specialist</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>recent graduate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -3247,12 +3255,12 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7735150003</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/phonepe</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3264,17 +3272,17 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>PhonePe</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Firmware Engineer(5-7 years)</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3284,7 +3292,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -3294,12 +3302,12 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7765845003</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/phonepe</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -3316,17 +3324,17 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>AI Video Specialist</t>
+          <t>Service Delivery Engineer, SRE</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>1-3 years</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -3341,7 +3349,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7735150003</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7762335003</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -3363,12 +3371,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Firmware Engineer(5-7 years)</t>
+          <t>Site Reliability Engineer - 2</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3388,7 +3396,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7765845003</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7766868003</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -3410,17 +3418,17 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Service Delivery Engineer</t>
+          <t>Software Engineer, Android</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>1-2 years</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -3435,7 +3443,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7766920003</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7799494003</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -3452,29 +3460,25 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>PhonePe</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Service Delivery Engineer, SRE</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1-3 years</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -3482,12 +3486,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7762335003</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/phonepe</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3499,17 +3503,17 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>PhonePe</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - 2</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3519,7 +3523,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -3529,12 +3533,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7766868003</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/phonepe</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3546,27 +3550,27 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>PhonePe</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Android</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>1-2 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -3576,12 +3580,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7799494003</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/phonepe</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -3593,17 +3597,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3611,7 +3615,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -3619,12 +3627,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3636,17 +3644,17 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3654,11 +3662,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -3666,12 +3670,12 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -3683,12 +3687,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -3703,7 +3707,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -3713,12 +3717,12 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -3730,17 +3734,17 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Full Stack Builder</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3750,7 +3754,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -3760,12 +3764,12 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3777,17 +3781,17 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Industrial Trainee</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3795,7 +3799,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -3803,12 +3811,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8083001?gh_jid=8083001</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -3820,12 +3828,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Payroll Industrial Trainee</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3840,7 +3848,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3850,12 +3858,12 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3867,17 +3875,17 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Sarvam AI</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Builder</t>
+          <t>Machine Learning Engineer, Vision</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3897,12 +3905,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</t>
+          <t>https://jobs.ashbyhq.com/sarvam/282019f4-f86b-4fe0-a643-bbac0cd8a751</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://jobs.ashbyhq.com/sarvam</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3914,17 +3922,17 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Industrial Trainee</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3934,7 +3942,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Remote Instructor- Python</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3944,12 +3952,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8083001?gh_jid=8083001</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3961,12 +3969,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Payroll Industrial Trainee</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -3979,11 +3987,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
       <c r="F77" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -3991,12 +3995,12 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTYsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -4008,17 +4012,17 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Sarvam AI</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Vision</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -4026,11 +4030,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam/282019f4-f86b-4fe0-a643-bbac0cd8a751</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -4055,29 +4055,25 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Sarvam AI</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer - Vision</t>
+          <t>Intern - Content Moderation(Tamil)</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1–2 years</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr"/>
       <c r="F79" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -4085,12 +4081,12 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam/5047b154-37f7-49df-9006-b52e8c79c0e9</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MDUsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4102,17 +4098,17 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Video Editor- AI</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -4120,11 +4116,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>Remote Instructor- Python</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
       <c r="F80" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -4132,12 +4124,12 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -4149,17 +4141,17 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -4167,7 +4159,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -4175,12 +4171,12 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTYsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -4192,17 +4188,17 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -4210,7 +4206,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr"/>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -4218,12 +4218,12 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -4235,17 +4235,17 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Snowflake India</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation(Tamil)</t>
+          <t>Account Engineer</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -4253,7 +4253,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>CO-Colombia-Remote</t>
+        </is>
+      </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -4261,12 +4265,12 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MDUsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://jobs.ashbyhq.com/snowflake</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -4278,17 +4282,17 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Video Editor- AI</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -4304,12 +4308,12 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -4321,17 +4325,17 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Test Jerin</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -4341,7 +4345,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -4351,12 +4355,12 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -4368,17 +4372,17 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -4388,7 +4392,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -4398,12 +4402,12 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
@@ -4415,12 +4419,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Snowflake India</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Account Engineer</t>
+          <t>Data Science Bootcamp with AI</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -4433,11 +4437,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>CO-Colombia-Remote</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
       <c r="F87" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
@@ -4445,12 +4445,12 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
+          <t>https://www.upgrad.com/bootcamps/job-linked-data-science-advanced-bootcamp/</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake</t>
+          <t>https://www.upgrad.com/careers/</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
@@ -4459,235 +4459,8 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>Sprinklr</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>Internship and Early Careers</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr"/>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>https://www.sprinklr.com/careers/</t>
-        </is>
-      </c>
-      <c r="I88" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>Twilio India</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>Associate Application Engineer</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>1 to 2 years</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>Remote - India</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/8048659</t>
-        </is>
-      </c>
-      <c r="H89" s="4" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/twilio</t>
-        </is>
-      </c>
-      <c r="I89" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>Test Jerin</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I90" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I91" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>upGrad</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>Data Science Bootcamp with AI</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr"/>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>https://www.upgrad.com/bootcamps/job-linked-data-science-advanced-bootcamp/</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>https://www.upgrad.com/careers/</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I92"/>
+  <autoFilter ref="A1:I87"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4775,11 +4548,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId91"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4791,7 +4559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4839,35 +4607,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Keka</t>
+          <t>Log9 Materials</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.keka.com/careers</t>
+          <t>https://www.log9materials.com/careers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.keka.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Log9 Materials</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.log9materials.com/careers</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4876,18 +4624,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4896,38 +4644,38 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BharatPe</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://bharatpe.com/careers</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: net::ERR_CERT_COMMON_NAME_INVALID at https://bharatpe.com/careers
+Call log:
+  - navigating to "https://bharatpe.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Vymo</t>
+          <t>Ather Energy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://getvymo.com/careers/</t>
+          <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://getvymo.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Ather Energy</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://www.atherenergy.com/careers</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4936,18 +4684,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -4956,38 +4704,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Darwinbox</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://darwinbox.com/careers</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://darwinbox.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4996,18 +4724,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5016,58 +4744,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Netcore Cloud</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://netcorecloud.com/careers/</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://netcorecloud.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Pocket FM</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://pocketfm.com/careers</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://pocketfm.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -5076,18 +4764,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -5096,18 +4784,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -5116,18 +4804,18 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5136,26 +4824,6 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Subex</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>https://www.subex.com/careers/</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.subex.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
